--- a/change_history.xlsx
+++ b/change_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,76 +458,1674 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Single Room</t>
+          <t>Double Room</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Single Room</t>
+          <t>Double Room</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Twin Room</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2027-01-17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2027-01-18</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2027-01-19</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2027-01-22</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2027-01-23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2027-01-24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2027-01-25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2027-01-26</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2027-01-27</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2027-01-28</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2027-01-29</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2027-01-30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2027-01-17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2027-01-18</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2027-01-19</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2027-01-22</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2027-01-23</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2027-01-24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2027-01-25</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2027-01-26</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2027-01-27</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2027-01-28</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2027-01-29</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2027-01-30</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2027-01-17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2027-01-18</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2027-01-19</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2027-01-22</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2027-01-23</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2027-01-24</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2027-01-25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2027-01-26</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2027-01-27</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2027-01-28</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2027-01-29</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2027-01-30</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2027-01-17</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2027-01-18</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2027-01-19</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2027-01-22</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2027-01-23</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2027-01-24</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2027-01-25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2027-01-26</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2027-01-27</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2027-01-28</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2027-01-29</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2027-01-30</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/change_history.xlsx
+++ b/change_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,22 +458,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Single Room</t>
+          <t>Twin Room</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -483,12 +483,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -496,66 +496,62 @@
           <t>Twin Room</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Twin Room</t>
+          <t>Double Room</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Twin Room</t>
+          <t>Double Room</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -565,22 +561,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -600,12 +596,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -625,17 +621,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Twin Room</t>
+          <t>Single Room</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -650,130 +646,138 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Twin Room</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Triple Room</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Triple Room</t>
+          <t>Single Room</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Single Room</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Single Room</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Twin Room</t>
+          <t>Single Room</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -782,43 +786,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Twin Room</t>
+          <t>Single Room</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -828,22 +832,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -851,20 +855,24 @@
           <t>Twin Room</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -872,20 +880,24 @@
           <t>Twin Room</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -895,464 +907,36 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Single Room</t>
+          <t>Twin Room</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Twin Room</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
         <v>8</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Twin Room</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Twin Room</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Triple Room</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Triple Room</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Triple Room</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Triple Room</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Triple Room</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Triple Room</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Triple Room</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Single Room</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Twin Room</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Twin Room</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Twin Room</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Single Room</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Single Room</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Single Room</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-11-22</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Single Room</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/change_history.xlsx
+++ b/change_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,12 +458,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -473,160 +473,170 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Twin Room</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Double Room</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Double Room</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Triple Room</t>
+          <t>Twin Room</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Triple Room</t>
+          <t>Twin Room</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Triple Room</t>
+          <t>Single Room</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -636,307 +646,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Triple Room</t>
+          <t>Single Room</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Single Room</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Single Room</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Triple Room</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Triple Room</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Single Room</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Single Room</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Twin Room</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Twin Room</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Twin Room</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Twin Room</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-01-23</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Twin Room</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/change_history.xlsx
+++ b/change_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,62 +458,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Twin Room</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Triple Room</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -521,24 +513,20 @@
           <t>Twin Room</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -546,24 +534,20 @@
           <t>Twin Room</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -571,111 +555,1192 @@
           <t>Twin Room</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Twin Room</t>
+          <t>Triple Room</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Single Room</t>
+          <t>Triple Room</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Single Room</t>
+          <t>Triple Room</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Single Room</t>
+          <t>Triple Room</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Twin Room</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/change_history.xlsx
+++ b/change_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,28 +458,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Single Room</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Triple Room</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -492,120 +496,116 @@
           <t>Single Room</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
-        <v>4</v>
-      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Triple Room</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Single Room</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Triple Room</t>
+          <t>Twin Room</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Triple Room</t>
+          <t>Twin Room</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Triple Room</t>
+          <t>Twin Room</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -625,12 +625,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -640,22 +640,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -665,22 +665,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>9</v>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -690,47 +688,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Twin Room</t>
+          <t>Single Room</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>6</v>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -740,7 +736,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -750,12 +746,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -773,12 +769,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -788,7 +784,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -796,12 +792,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -815,6 +811,100 @@
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Double Room</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
